--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DESTOP\工具\选择器更新\data\"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
   <si>
     <t>SKU</t>
   </si>
@@ -43,6 +43,9 @@
     <t>LINK</t>
   </si>
   <si>
+    <t>本地路径</t>
+  </si>
+  <si>
     <t>RTS-AU-SIMPORTAL-MAX-M1</t>
   </si>
   <si>
@@ -50,6 +53,18 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/19YV6YD_WhfrDHW35PPm0GKtKf858cHt1/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>RTS-SR-LVL-7-ZM-P2</t>
+  </si>
+  <si>
+    <t>zm</t>
+  </si>
+  <si>
+    <t>RTS-SR-LVL-7-ZM-P2.png</t>
   </si>
 </sst>
 </file>
@@ -62,18 +77,26 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
+  <fonts count="22">
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="等线"/>
+      <sz val="9.75"/>
+      <color rgb="FF2C2F32"/>
+      <name val="Roboto"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -522,161 +545,155 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -729,221 +746,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -953,7 +756,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -963,46 +766,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1033,11 +836,11 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1074,151 +877,216 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="30.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="63.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="96.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="32.8333333333333" customWidth="1"/>
+    <col min="2" max="2" width="52.8333333333333" customWidth="1"/>
+    <col min="3" max="3" width="64.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="80.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1228,44 +1096,113 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="C3 A1:C1 A2:D2 A4:D8" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>